--- a/test_data/simulations_R/simulations_complexity.xlsx
+++ b/test_data/simulations_R/simulations_complexity.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/labanfibios/Desktop/Doutorado/Project/B3_PrepDyn/GitHub/test_data/simulations_R/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00C67C2-5447-8A43-A4B2-182E773F8929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D70485-5EDC-4B4E-BF82-2FE0CA51B1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="18040" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="18040" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="without80t" sheetId="1" r:id="rId1"/>
-    <sheet name="with80t" sheetId="2" r:id="rId2"/>
+    <sheet name="final" sheetId="3" r:id="rId1"/>
+    <sheet name="without80t" sheetId="1" r:id="rId2"/>
+    <sheet name="with80t" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="112">
   <si>
     <t>n_partitions</t>
   </si>
@@ -1300,6 +1301,2796 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3803390F-27DD-6242-9536-D7107CDDA9EC}">
+  <dimension ref="A1:N61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+      <c r="G2">
+        <v>997</v>
+      </c>
+      <c r="H2">
+        <v>3.5669999999999999E-3</v>
+      </c>
+      <c r="I2">
+        <v>3.6971600000000001E-3</v>
+      </c>
+      <c r="J2">
+        <v>346</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2" s="11">
+        <v>188.08699999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3">
+        <v>9997</v>
+      </c>
+      <c r="H3">
+        <v>2.6887999999999999E-2</v>
+      </c>
+      <c r="I3">
+        <v>2.716184E-2</v>
+      </c>
+      <c r="J3" s="7">
+        <v>3357</v>
+      </c>
+      <c r="K3" s="7">
+        <v>3</v>
+      </c>
+      <c r="L3" s="7">
+        <v>2655.9209999999998</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>10000</v>
+      </c>
+      <c r="G4">
+        <v>99600</v>
+      </c>
+      <c r="H4">
+        <v>0.32880700000000002</v>
+      </c>
+      <c r="I4">
+        <v>0.41839099000000002</v>
+      </c>
+      <c r="J4" s="16">
+        <v>33266</v>
+      </c>
+      <c r="K4" s="16">
+        <v>2</v>
+      </c>
+      <c r="L4" s="16">
+        <v>34746.883999999998</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>1987</v>
+      </c>
+      <c r="H5">
+        <v>5.8729999999999997E-3</v>
+      </c>
+      <c r="I5">
+        <v>6.9060299999999996E-3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>685</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2551.1529999999998</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="G6">
+        <v>19983</v>
+      </c>
+      <c r="H6">
+        <v>4.9492000000000001E-2</v>
+      </c>
+      <c r="I6">
+        <v>5.05631E-2</v>
+      </c>
+      <c r="J6" s="6">
+        <v>6991</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6">
+        <v>29482.580999999998</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>10000</v>
+      </c>
+      <c r="G7">
+        <v>198677</v>
+      </c>
+      <c r="H7">
+        <v>0.50287000000000004</v>
+      </c>
+      <c r="I7">
+        <v>0.51095389999999996</v>
+      </c>
+      <c r="J7" s="15">
+        <v>69332</v>
+      </c>
+      <c r="K7" s="15">
+        <v>1</v>
+      </c>
+      <c r="L7" s="15">
+        <v>390118.52399999998</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>3965</v>
+      </c>
+      <c r="H8">
+        <v>1.1343000000000001E-2</v>
+      </c>
+      <c r="I8">
+        <v>1.212907E-2</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1412</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2">
+        <v>18695.815999999999</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>1000</v>
+      </c>
+      <c r="G9">
+        <v>39907</v>
+      </c>
+      <c r="H9">
+        <v>9.2376E-2</v>
+      </c>
+      <c r="I9">
+        <v>9.4183920000000004E-2</v>
+      </c>
+      <c r="J9" s="14">
+        <v>14132</v>
+      </c>
+      <c r="K9" s="14">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14">
+        <v>278214.19300000003</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>10000</v>
+      </c>
+      <c r="G10">
+        <v>396791</v>
+      </c>
+      <c r="H10">
+        <v>0.96195600000000003</v>
+      </c>
+      <c r="I10">
+        <v>0.98200273999999999</v>
+      </c>
+      <c r="J10" s="4">
+        <v>139786</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1</v>
+      </c>
+      <c r="L10" s="4">
+        <v>45338656.719999999</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>80</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>7916</v>
+      </c>
+      <c r="H11">
+        <v>2.0653999999999999E-2</v>
+      </c>
+      <c r="I11">
+        <v>2.0794150000000001E-2</v>
+      </c>
+      <c r="J11" s="13">
+        <v>2685</v>
+      </c>
+      <c r="K11" s="13">
+        <v>1</v>
+      </c>
+      <c r="L11" s="13">
+        <v>210979.57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="F12">
+        <v>1000</v>
+      </c>
+      <c r="G12">
+        <v>78657</v>
+      </c>
+      <c r="H12">
+        <v>0.19187699999999999</v>
+      </c>
+      <c r="I12">
+        <v>0.19801497000000001</v>
+      </c>
+      <c r="J12" s="3">
+        <v>26267</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2671616.8859999999</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>80</v>
+      </c>
+      <c r="F13">
+        <v>10000</v>
+      </c>
+      <c r="G13">
+        <v>791251</v>
+      </c>
+      <c r="H13">
+        <v>2.0672540000000001</v>
+      </c>
+      <c r="I13">
+        <v>2.3659317500000001</v>
+      </c>
+      <c r="J13" s="1">
+        <v>263185</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>42494919.780000001</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>100</v>
+      </c>
+      <c r="G14">
+        <v>997</v>
+      </c>
+      <c r="H14">
+        <v>3.8660000000000001E-3</v>
+      </c>
+      <c r="I14">
+        <v>4.0888799999999996E-3</v>
+      </c>
+      <c r="J14">
+        <v>348</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" s="11">
+        <v>236.649</v>
+      </c>
+      <c r="M14">
+        <f>J14-J2</f>
+        <v>2</v>
+      </c>
+      <c r="N14">
+        <f>L14-L2</f>
+        <v>48.562000000000012</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>1000</v>
+      </c>
+      <c r="G15">
+        <v>9997</v>
+      </c>
+      <c r="H15">
+        <v>2.8990999999999999E-2</v>
+      </c>
+      <c r="I15">
+        <v>2.908635E-2</v>
+      </c>
+      <c r="J15" s="7">
+        <v>3358</v>
+      </c>
+      <c r="K15" s="7">
+        <v>2</v>
+      </c>
+      <c r="L15" s="7">
+        <v>1878.2190000000001</v>
+      </c>
+      <c r="M15">
+        <f>J15-J3</f>
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <f t="shared" ref="N15:N61" si="0">L15-L3</f>
+        <v>-777.70199999999977</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10000</v>
+      </c>
+      <c r="G16">
+        <v>99600</v>
+      </c>
+      <c r="H16">
+        <v>0.27939399999999998</v>
+      </c>
+      <c r="I16">
+        <v>0.28424788000000001</v>
+      </c>
+      <c r="J16" s="16">
+        <v>33279</v>
+      </c>
+      <c r="K16" s="16">
+        <v>2</v>
+      </c>
+      <c r="L16" s="16">
+        <v>33028.516000000003</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ref="M16:M61" si="1">J16-J4</f>
+        <v>13</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="0"/>
+        <v>-1718.3679999999949</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>100</v>
+      </c>
+      <c r="G17">
+        <v>1987</v>
+      </c>
+      <c r="H17">
+        <v>7.6499999999999997E-3</v>
+      </c>
+      <c r="I17">
+        <v>8.3968600000000008E-3</v>
+      </c>
+      <c r="J17" s="5">
+        <v>693</v>
+      </c>
+      <c r="K17" s="5">
+        <v>1</v>
+      </c>
+      <c r="L17" s="5">
+        <v>2986.0479999999998</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="0"/>
+        <v>434.89499999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>20</v>
+      </c>
+      <c r="F18">
+        <v>1000</v>
+      </c>
+      <c r="G18">
+        <v>19983</v>
+      </c>
+      <c r="H18">
+        <v>5.1749000000000003E-2</v>
+      </c>
+      <c r="I18">
+        <v>5.3464890000000001E-2</v>
+      </c>
+      <c r="J18" s="6">
+        <v>7011</v>
+      </c>
+      <c r="K18" s="6">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6">
+        <v>28005.481</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="0"/>
+        <v>-1477.0999999999985</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="F19">
+        <v>10000</v>
+      </c>
+      <c r="G19">
+        <v>198677</v>
+      </c>
+      <c r="H19">
+        <v>0.51940500000000001</v>
+      </c>
+      <c r="I19">
+        <v>0.53595113999999999</v>
+      </c>
+      <c r="J19" s="15">
+        <v>69392</v>
+      </c>
+      <c r="K19" s="15">
+        <v>2</v>
+      </c>
+      <c r="L19" s="15">
+        <v>357179.10200000001</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="0"/>
+        <v>-32939.421999999962</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>40</v>
+      </c>
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20">
+        <v>3965</v>
+      </c>
+      <c r="H20">
+        <v>1.0441000000000001E-2</v>
+      </c>
+      <c r="I20">
+        <v>1.058602E-2</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1420</v>
+      </c>
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2">
+        <v>21790.026000000002</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="0"/>
+        <v>3094.2100000000028</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>40</v>
+      </c>
+      <c r="F21">
+        <v>1000</v>
+      </c>
+      <c r="G21">
+        <v>39907</v>
+      </c>
+      <c r="H21">
+        <v>9.9750000000000005E-2</v>
+      </c>
+      <c r="I21">
+        <v>0.10255694</v>
+      </c>
+      <c r="J21" s="14">
+        <v>14174</v>
+      </c>
+      <c r="K21" s="14">
+        <v>1</v>
+      </c>
+      <c r="L21" s="14">
+        <v>289712.07900000003</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="0"/>
+        <v>11497.885999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>10000</v>
+      </c>
+      <c r="G22">
+        <v>396791</v>
+      </c>
+      <c r="H22">
+        <v>0.93147400000000002</v>
+      </c>
+      <c r="I22">
+        <v>0.93528317999999999</v>
+      </c>
+      <c r="J22" s="4">
+        <v>139940</v>
+      </c>
+      <c r="K22" s="4">
+        <v>1</v>
+      </c>
+      <c r="L22" s="4">
+        <v>3905536.0529999998</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="0"/>
+        <v>-41433120.666999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>80</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>7916</v>
+      </c>
+      <c r="H23">
+        <v>2.0031E-2</v>
+      </c>
+      <c r="I23">
+        <v>2.0530940000000001E-2</v>
+      </c>
+      <c r="J23" s="13">
+        <v>2730</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="13">
+        <v>232603.261</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="0"/>
+        <v>21623.690999999992</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>80</v>
+      </c>
+      <c r="F24">
+        <v>1000</v>
+      </c>
+      <c r="G24">
+        <v>78657</v>
+      </c>
+      <c r="H24">
+        <v>0.18313499999999999</v>
+      </c>
+      <c r="I24">
+        <v>0.18543506000000001</v>
+      </c>
+      <c r="J24" s="3">
+        <v>26350</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3">
+        <v>2827274.4309999999</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="0"/>
+        <v>155657.54499999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>80</v>
+      </c>
+      <c r="F25">
+        <v>10000</v>
+      </c>
+      <c r="G25">
+        <v>791251</v>
+      </c>
+      <c r="H25">
+        <v>1.914431</v>
+      </c>
+      <c r="I25">
+        <v>1.9443078</v>
+      </c>
+      <c r="J25" s="1">
+        <v>263235</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="12">
+        <v>37900000</v>
+      </c>
+      <c r="M25">
+        <f>J25-J13</f>
+        <v>50</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="0"/>
+        <v>-4594919.7800000012</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
+        <v>997</v>
+      </c>
+      <c r="H26">
+        <v>5.7159999999999997E-3</v>
+      </c>
+      <c r="I26">
+        <v>5.9258899999999996E-3</v>
+      </c>
+      <c r="J26">
+        <v>354</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="11">
+        <v>279.27300000000002</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="0"/>
+        <v>42.624000000000024</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>1000</v>
+      </c>
+      <c r="G27">
+        <v>9997</v>
+      </c>
+      <c r="H27">
+        <v>2.6468999999999999E-2</v>
+      </c>
+      <c r="I27">
+        <v>2.6546E-2</v>
+      </c>
+      <c r="J27" s="7">
+        <v>3372</v>
+      </c>
+      <c r="K27" s="7">
+        <v>4</v>
+      </c>
+      <c r="L27" s="7">
+        <v>1964.9770000000001</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="0"/>
+        <v>86.758000000000038</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>10000</v>
+      </c>
+      <c r="G28">
+        <v>99600</v>
+      </c>
+      <c r="H28">
+        <v>0.28694700000000001</v>
+      </c>
+      <c r="I28">
+        <v>0.30184817000000003</v>
+      </c>
+      <c r="J28" s="16">
+        <v>33303</v>
+      </c>
+      <c r="K28" s="16">
+        <v>2</v>
+      </c>
+      <c r="L28" s="16">
+        <v>20333.065999999999</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="0"/>
+        <v>-12695.450000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>20</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>1987</v>
+      </c>
+      <c r="H29">
+        <v>8.6650000000000008E-3</v>
+      </c>
+      <c r="I29">
+        <v>9.4437600000000007E-3</v>
+      </c>
+      <c r="J29" s="5">
+        <v>703</v>
+      </c>
+      <c r="K29" s="5">
+        <v>1</v>
+      </c>
+      <c r="L29" s="5">
+        <v>2198.3649999999998</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="0"/>
+        <v>-787.68299999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30">
+        <v>20</v>
+      </c>
+      <c r="F30">
+        <v>1000</v>
+      </c>
+      <c r="G30">
+        <v>19983</v>
+      </c>
+      <c r="H30">
+        <v>4.8845E-2</v>
+      </c>
+      <c r="I30">
+        <v>4.9627070000000002E-2</v>
+      </c>
+      <c r="J30" s="6">
+        <v>7046</v>
+      </c>
+      <c r="K30" s="6">
+        <v>1</v>
+      </c>
+      <c r="L30" s="6">
+        <v>28775.846000000001</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="0"/>
+        <v>770.3650000000016</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>10000</v>
+      </c>
+      <c r="G31">
+        <v>198677</v>
+      </c>
+      <c r="H31">
+        <v>0.52512599999999998</v>
+      </c>
+      <c r="I31">
+        <v>0.53225803000000005</v>
+      </c>
+      <c r="J31" s="15">
+        <v>69415</v>
+      </c>
+      <c r="K31" s="15">
+        <v>1</v>
+      </c>
+      <c r="L31" s="15">
+        <v>296511.65600000002</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="0"/>
+        <v>-60667.445999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32">
+        <v>40</v>
+      </c>
+      <c r="F32">
+        <v>100</v>
+      </c>
+      <c r="G32">
+        <v>3965</v>
+      </c>
+      <c r="H32">
+        <v>1.0083999999999999E-2</v>
+      </c>
+      <c r="I32">
+        <v>1.010609E-2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1449</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2">
+        <v>25535.506000000001</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="0"/>
+        <v>3745.4799999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>40</v>
+      </c>
+      <c r="F33">
+        <v>1000</v>
+      </c>
+      <c r="G33">
+        <v>39907</v>
+      </c>
+      <c r="H33">
+        <v>9.6226000000000006E-2</v>
+      </c>
+      <c r="I33">
+        <v>9.8910090000000006E-2</v>
+      </c>
+      <c r="J33" s="14">
+        <v>14246</v>
+      </c>
+      <c r="K33" s="14">
+        <v>1</v>
+      </c>
+      <c r="L33" s="14">
+        <v>254567.21599999999</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="0"/>
+        <v>-35144.863000000041</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>40</v>
+      </c>
+      <c r="F34">
+        <v>10000</v>
+      </c>
+      <c r="G34">
+        <v>396791</v>
+      </c>
+      <c r="H34">
+        <v>0.96683200000000002</v>
+      </c>
+      <c r="I34">
+        <v>0.98024106</v>
+      </c>
+      <c r="J34" s="4">
+        <v>139955</v>
+      </c>
+      <c r="K34" s="4">
+        <v>1</v>
+      </c>
+      <c r="L34" s="4">
+        <v>3287602.4130000002</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="0"/>
+        <v>-617933.63999999966</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>80</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>7916</v>
+      </c>
+      <c r="H35">
+        <v>2.0459999999999999E-2</v>
+      </c>
+      <c r="I35">
+        <v>2.1188019999999998E-2</v>
+      </c>
+      <c r="J35" s="13">
+        <v>2721</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="13">
+        <v>280824.21299999999</v>
+      </c>
+      <c r="M35">
+        <f>J35-J23</f>
+        <v>-9</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="0"/>
+        <v>48220.95199999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>80</v>
+      </c>
+      <c r="F36">
+        <v>1000</v>
+      </c>
+      <c r="G36">
+        <v>78657</v>
+      </c>
+      <c r="H36">
+        <v>0.19505700000000001</v>
+      </c>
+      <c r="I36">
+        <v>0.19804478</v>
+      </c>
+      <c r="J36" s="3">
+        <v>26424</v>
+      </c>
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3">
+        <v>2449525.5249999999</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="0"/>
+        <v>-377748.90599999996</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>80</v>
+      </c>
+      <c r="F37">
+        <v>10000</v>
+      </c>
+      <c r="G37">
+        <v>791251</v>
+      </c>
+      <c r="H37">
+        <v>2.0209060000000001</v>
+      </c>
+      <c r="I37">
+        <v>2.18471408</v>
+      </c>
+      <c r="J37" s="1">
+        <v>263377</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="12">
+        <v>34286475.689999998</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="1"/>
+        <v>142</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="0"/>
+        <v>-3613524.3100000024</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>997</v>
+      </c>
+      <c r="H38">
+        <v>3.3670000000000002E-3</v>
+      </c>
+      <c r="I38">
+        <v>3.3659900000000001E-3</v>
+      </c>
+      <c r="J38">
+        <v>357</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+      <c r="L38" s="11">
+        <v>280.84100000000001</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="0"/>
+        <v>1.5679999999999836</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>1000</v>
+      </c>
+      <c r="G39">
+        <v>9997</v>
+      </c>
+      <c r="H39">
+        <v>2.7307000000000001E-2</v>
+      </c>
+      <c r="I39">
+        <v>2.75619E-2</v>
+      </c>
+      <c r="J39" s="7">
+        <v>3367</v>
+      </c>
+      <c r="K39" s="7">
+        <v>3</v>
+      </c>
+      <c r="L39" s="7">
+        <v>2376.107</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="1"/>
+        <v>-5</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="0"/>
+        <v>411.12999999999988</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="F40">
+        <v>10000</v>
+      </c>
+      <c r="G40">
+        <v>99600</v>
+      </c>
+      <c r="H40">
+        <v>0.29297600000000001</v>
+      </c>
+      <c r="I40">
+        <v>0.30019212000000001</v>
+      </c>
+      <c r="J40" s="16">
+        <v>33332</v>
+      </c>
+      <c r="K40" s="16">
+        <v>2</v>
+      </c>
+      <c r="L40" s="16">
+        <v>24581.168000000001</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="0"/>
+        <v>4248.1020000000026</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>20</v>
+      </c>
+      <c r="F41">
+        <v>100</v>
+      </c>
+      <c r="G41">
+        <v>1987</v>
+      </c>
+      <c r="H41">
+        <v>5.5459999999999997E-3</v>
+      </c>
+      <c r="I41">
+        <v>5.5470500000000004E-3</v>
+      </c>
+      <c r="J41" s="5">
+        <v>713</v>
+      </c>
+      <c r="K41" s="5">
+        <v>1</v>
+      </c>
+      <c r="L41" s="5">
+        <v>3200.8090000000002</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="0"/>
+        <v>1002.4440000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42">
+        <v>20</v>
+      </c>
+      <c r="F42">
+        <v>1000</v>
+      </c>
+      <c r="G42">
+        <v>19983</v>
+      </c>
+      <c r="H42">
+        <v>5.3247999999999997E-2</v>
+      </c>
+      <c r="I42">
+        <v>5.4213049999999999E-2</v>
+      </c>
+      <c r="J42" s="6">
+        <v>7068</v>
+      </c>
+      <c r="K42" s="6">
+        <v>1</v>
+      </c>
+      <c r="L42" s="6">
+        <v>27242.362000000001</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="0"/>
+        <v>-1533.4840000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>20</v>
+      </c>
+      <c r="F43">
+        <v>10000</v>
+      </c>
+      <c r="G43">
+        <v>198677</v>
+      </c>
+      <c r="H43">
+        <v>0.48879499999999998</v>
+      </c>
+      <c r="I43">
+        <v>0.49281978999999998</v>
+      </c>
+      <c r="J43" s="15">
+        <v>69489</v>
+      </c>
+      <c r="K43" s="15">
+        <v>1</v>
+      </c>
+      <c r="L43" s="15">
+        <v>315767.81300000002</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="0"/>
+        <v>19256.157000000007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>40</v>
+      </c>
+      <c r="F44">
+        <v>100</v>
+      </c>
+      <c r="G44">
+        <v>3965</v>
+      </c>
+      <c r="H44">
+        <v>1.0599000000000001E-2</v>
+      </c>
+      <c r="I44">
+        <v>1.083803E-2</v>
+      </c>
+      <c r="J44" s="2">
+        <v>1461</v>
+      </c>
+      <c r="K44" s="2">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2">
+        <v>28993.989000000001</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="0"/>
+        <v>3458.4830000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
+      </c>
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>40</v>
+      </c>
+      <c r="F45">
+        <v>1000</v>
+      </c>
+      <c r="G45">
+        <v>39907</v>
+      </c>
+      <c r="H45">
+        <v>9.2087000000000002E-2</v>
+      </c>
+      <c r="I45">
+        <v>9.2258930000000003E-2</v>
+      </c>
+      <c r="J45" s="14">
+        <v>14330</v>
+      </c>
+      <c r="K45" s="14">
+        <v>1</v>
+      </c>
+      <c r="L45" s="14">
+        <v>269092.35499999998</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="0"/>
+        <v>14525.138999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46">
+        <v>40</v>
+      </c>
+      <c r="F46">
+        <v>10000</v>
+      </c>
+      <c r="G46">
+        <v>396791</v>
+      </c>
+      <c r="H46">
+        <v>0.94772500000000004</v>
+      </c>
+      <c r="I46">
+        <v>0.95472908000000001</v>
+      </c>
+      <c r="J46" s="4">
+        <v>140173</v>
+      </c>
+      <c r="K46" s="4">
+        <v>1</v>
+      </c>
+      <c r="L46" s="4">
+        <v>2955897.6979999999</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="1"/>
+        <v>218</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="0"/>
+        <v>-331704.71500000032</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>80</v>
+      </c>
+      <c r="F47">
+        <v>100</v>
+      </c>
+      <c r="G47">
+        <v>7916</v>
+      </c>
+      <c r="H47">
+        <v>2.1644E-2</v>
+      </c>
+      <c r="I47">
+        <v>2.2154090000000001E-2</v>
+      </c>
+      <c r="J47" s="13">
+        <v>2773</v>
+      </c>
+      <c r="K47" s="13">
+        <v>1</v>
+      </c>
+      <c r="L47" s="13">
+        <v>261753.77900000001</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="0"/>
+        <v>-19070.433999999979</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>80</v>
+      </c>
+      <c r="F48">
+        <v>1000</v>
+      </c>
+      <c r="G48">
+        <v>78657</v>
+      </c>
+      <c r="H48">
+        <v>0.18748200000000001</v>
+      </c>
+      <c r="I48">
+        <v>0.18853974000000001</v>
+      </c>
+      <c r="J48" s="3">
+        <v>26530</v>
+      </c>
+      <c r="K48" s="3">
+        <v>1</v>
+      </c>
+      <c r="L48" s="3">
+        <v>2620800.5060000001</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="0"/>
+        <v>171274.98100000015</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49">
+        <v>5</v>
+      </c>
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49">
+        <v>80</v>
+      </c>
+      <c r="F49">
+        <v>10000</v>
+      </c>
+      <c r="G49">
+        <v>791251</v>
+      </c>
+      <c r="H49">
+        <v>1.9845900000000001</v>
+      </c>
+      <c r="I49">
+        <v>2.0390899199999999</v>
+      </c>
+      <c r="J49" s="1">
+        <v>263756</v>
+      </c>
+      <c r="K49" s="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>33568826.344999999</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="1"/>
+        <v>379</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="0"/>
+        <v>-717649.34499999881</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50">
+        <v>9</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50">
+        <v>100</v>
+      </c>
+      <c r="G50">
+        <v>997</v>
+      </c>
+      <c r="H50">
+        <v>3.4970000000000001E-3</v>
+      </c>
+      <c r="I50">
+        <v>3.4968899999999999E-3</v>
+      </c>
+      <c r="J50">
+        <v>362</v>
+      </c>
+      <c r="K50">
+        <v>4</v>
+      </c>
+      <c r="L50" s="11">
+        <v>333.63400000000001</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="0"/>
+        <v>52.793000000000006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>10</v>
+      </c>
+      <c r="F51">
+        <v>1000</v>
+      </c>
+      <c r="G51">
+        <v>9997</v>
+      </c>
+      <c r="H51">
+        <v>2.6551999999999999E-2</v>
+      </c>
+      <c r="I51">
+        <v>2.656698E-2</v>
+      </c>
+      <c r="J51" s="7">
+        <v>3398</v>
+      </c>
+      <c r="K51" s="7">
+        <v>3</v>
+      </c>
+      <c r="L51" s="7">
+        <v>2938.3180000000002</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="0"/>
+        <v>562.21100000000024</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>8</v>
+      </c>
+      <c r="E52">
+        <v>10</v>
+      </c>
+      <c r="F52">
+        <v>10000</v>
+      </c>
+      <c r="G52">
+        <v>99600</v>
+      </c>
+      <c r="H52">
+        <v>0.266816</v>
+      </c>
+      <c r="I52">
+        <v>0.26821113000000002</v>
+      </c>
+      <c r="J52" s="16">
+        <v>33372</v>
+      </c>
+      <c r="K52" s="16">
+        <v>2</v>
+      </c>
+      <c r="L52" s="16">
+        <v>24548.451000000001</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="0"/>
+        <v>-32.717000000000553</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <v>100</v>
+      </c>
+      <c r="G53">
+        <v>1987</v>
+      </c>
+      <c r="H53">
+        <v>5.9230000000000003E-3</v>
+      </c>
+      <c r="I53">
+        <v>5.9766799999999998E-3</v>
+      </c>
+      <c r="J53" s="5">
+        <v>735</v>
+      </c>
+      <c r="K53" s="5">
+        <v>1</v>
+      </c>
+      <c r="L53" s="5">
+        <v>3408.1559999999999</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="0"/>
+        <v>207.34699999999975</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54">
+        <v>9</v>
+      </c>
+      <c r="D54">
+        <v>8</v>
+      </c>
+      <c r="E54">
+        <v>20</v>
+      </c>
+      <c r="F54">
+        <v>1000</v>
+      </c>
+      <c r="G54">
+        <v>19983</v>
+      </c>
+      <c r="H54">
+        <v>5.0900000000000001E-2</v>
+      </c>
+      <c r="I54">
+        <v>5.166602E-2</v>
+      </c>
+      <c r="J54" s="6">
+        <v>7126</v>
+      </c>
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="6">
+        <v>25231.822</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="0"/>
+        <v>-2010.5400000000009</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>8</v>
+      </c>
+      <c r="E55">
+        <v>20</v>
+      </c>
+      <c r="F55">
+        <v>10000</v>
+      </c>
+      <c r="G55">
+        <v>198677</v>
+      </c>
+      <c r="H55">
+        <v>0.490371</v>
+      </c>
+      <c r="I55">
+        <v>0.49296688999999999</v>
+      </c>
+      <c r="J55" s="15">
+        <v>69610</v>
+      </c>
+      <c r="K55" s="15">
+        <v>1</v>
+      </c>
+      <c r="L55" s="15">
+        <v>286165.16700000002</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="0"/>
+        <v>-29602.646000000008</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56">
+        <v>9</v>
+      </c>
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56">
+        <v>40</v>
+      </c>
+      <c r="F56">
+        <v>100</v>
+      </c>
+      <c r="G56">
+        <v>3965</v>
+      </c>
+      <c r="H56">
+        <v>1.1346999999999999E-2</v>
+      </c>
+      <c r="I56">
+        <v>1.188374E-2</v>
+      </c>
+      <c r="J56" s="2">
+        <v>1508</v>
+      </c>
+      <c r="K56" s="2">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2">
+        <v>31647.780999999999</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="0"/>
+        <v>2653.7919999999976</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57">
+        <v>9</v>
+      </c>
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57">
+        <v>40</v>
+      </c>
+      <c r="F57">
+        <v>1000</v>
+      </c>
+      <c r="G57">
+        <v>39907</v>
+      </c>
+      <c r="H57">
+        <v>9.1229000000000005E-2</v>
+      </c>
+      <c r="I57">
+        <v>9.1556070000000003E-2</v>
+      </c>
+      <c r="J57" s="14">
+        <v>14442</v>
+      </c>
+      <c r="K57" s="14">
+        <v>1</v>
+      </c>
+      <c r="L57" s="14">
+        <v>264146.01400000002</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="0"/>
+        <v>-4946.3409999999567</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58">
+        <v>9</v>
+      </c>
+      <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58">
+        <v>40</v>
+      </c>
+      <c r="F58">
+        <v>10000</v>
+      </c>
+      <c r="G58">
+        <v>396791</v>
+      </c>
+      <c r="H58">
+        <v>0.91834300000000002</v>
+      </c>
+      <c r="I58">
+        <v>0.92203212000000001</v>
+      </c>
+      <c r="J58" s="4">
+        <v>140425</v>
+      </c>
+      <c r="K58" s="4">
+        <v>1</v>
+      </c>
+      <c r="L58" s="4">
+        <v>2942548.9959999998</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="1"/>
+        <v>252</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="0"/>
+        <v>-13348.702000000048</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59">
+        <v>80</v>
+      </c>
+      <c r="F59">
+        <v>100</v>
+      </c>
+      <c r="G59">
+        <v>7916</v>
+      </c>
+      <c r="H59">
+        <v>2.2168E-2</v>
+      </c>
+      <c r="I59">
+        <v>2.246714E-2</v>
+      </c>
+      <c r="J59" s="13">
+        <v>2848</v>
+      </c>
+      <c r="K59" s="13">
+        <v>1</v>
+      </c>
+      <c r="L59" s="13">
+        <v>292444.967</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="0"/>
+        <v>30691.187999999995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60">
+        <v>9</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60">
+        <v>80</v>
+      </c>
+      <c r="F60">
+        <v>1000</v>
+      </c>
+      <c r="G60">
+        <v>78657</v>
+      </c>
+      <c r="H60">
+        <v>0.181587</v>
+      </c>
+      <c r="I60">
+        <v>0.18158102000000001</v>
+      </c>
+      <c r="J60" s="3">
+        <v>26722</v>
+      </c>
+      <c r="K60" s="3">
+        <v>1</v>
+      </c>
+      <c r="L60" s="3">
+        <v>2727788</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="1"/>
+        <v>192</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="0"/>
+        <v>106987.49399999995</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>8</v>
+      </c>
+      <c r="E61">
+        <v>80</v>
+      </c>
+      <c r="F61">
+        <v>10000</v>
+      </c>
+      <c r="G61">
+        <v>791251</v>
+      </c>
+      <c r="H61">
+        <v>1.8331789999999999</v>
+      </c>
+      <c r="I61">
+        <v>1.84392405</v>
+      </c>
+      <c r="J61" s="1">
+        <v>264187</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1</v>
+      </c>
+      <c r="L61" s="12">
+        <v>29569355.620999999</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="1"/>
+        <v>431</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="0"/>
+        <v>-3999470.7239999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4437,7 +7228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
